--- a/output/daily_ratings/uk_ratings_2026-06-07.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-06-07.xlsx
@@ -524,34 +524,36 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mister Bluebird</t>
+          <t>Toyotomi (FR)</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="K2" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>73.92</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>86.2</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -580,34 +582,38 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Solar Aclaim (IRE)</t>
+          <t>Sudden Flight</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K3" t="n">
-        <v>86</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M3" t="n">
         <v>73.92</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>80.5</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -636,28 +642,30 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Toyotomi (FR)</t>
+          <t>Fleetwater</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="K4" t="n">
-        <v>92</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3</v>
+      </c>
       <c r="M4" t="n">
         <v>73.92</v>
       </c>
       <c r="N4" t="n">
-        <v>86.2</v>
+        <v>76.5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -665,7 +673,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -694,30 +702,30 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sudden Flight</t>
+          <t>Sturlasson (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L5" t="n">
-        <v>0.15</v>
+        <v>0.4499999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>73.92</v>
       </c>
       <c r="N5" t="n">
-        <v>80.5</v>
+        <v>78.7</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -725,7 +733,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -754,30 +762,30 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fleetwater</t>
+          <t>Jungle Drums (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="K6" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
         <v>73.92</v>
       </c>
       <c r="N6" t="n">
-        <v>76.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -785,7 +793,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -814,30 +822,30 @@
         <v>3</v>
       </c>
       <c r="G7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Brosay</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sturlasson (IRE)</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
       <c r="J7" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K7" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L7" t="n">
-        <v>0.45</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
         <v>73.92</v>
       </c>
       <c r="N7" t="n">
-        <v>78.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -845,7 +853,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -874,30 +882,30 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jungle Drums (IRE)</t>
+          <t>Seven Questions (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K8" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>7.850000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>73.92</v>
       </c>
       <c r="N8" t="n">
-        <v>73.59999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -933,40 +941,24 @@
       <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
-        <v>6</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Brosay</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>134</v>
-      </c>
-      <c r="K9" t="n">
-        <v>89</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="M9" t="n">
-        <v>73.92</v>
-      </c>
-      <c r="N9" t="n">
-        <v>72.90000000000001</v>
-      </c>
+          <t>Mister Bluebird</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,40 +985,24 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>7</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Seven Questions (IRE)</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>135</v>
-      </c>
-      <c r="K10" t="n">
-        <v>90</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="M10" t="n">
-        <v>73.92</v>
-      </c>
-      <c r="N10" t="n">
-        <v>58.8</v>
-      </c>
+          <t>Solar Aclaim (IRE)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1710,11 +1686,11 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Botagoz (IRE)</t>
+          <t>Venetia</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1724,20 +1700,22 @@
         <v>128</v>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>134.27</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>62.8</v>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-9.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="23">
@@ -1766,11 +1744,11 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Capichera (IRE)</t>
+          <t>Lady Dora Mae (IRE)</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1780,20 +1758,24 @@
         <v>128</v>
       </c>
       <c r="K23" t="n">
-        <v>82</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.05</v>
+      </c>
       <c r="M23" t="n">
         <v>134.27</v>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>63.3</v>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1822,11 +1804,11 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Venetia</t>
+          <t>Della Pace</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1836,14 +1818,16 @@
         <v>128</v>
       </c>
       <c r="K24" t="n">
-        <v>82</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M24" t="n">
         <v>134.27</v>
       </c>
       <c r="N24" t="n">
-        <v>62.8</v>
+        <v>63.5</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1851,7 +1835,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1880,11 +1864,11 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lady Dora Mae (IRE)</t>
+          <t>Sacred Ground</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1894,16 +1878,16 @@
         <v>128</v>
       </c>
       <c r="K25" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="L25" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="M25" t="n">
         <v>134.27</v>
       </c>
       <c r="N25" t="n">
-        <v>63.3</v>
+        <v>62.9</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1911,7 +1895,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1940,11 +1924,11 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Della Pace</t>
+          <t>Plaid</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1954,16 +1938,16 @@
         <v>128</v>
       </c>
       <c r="K26" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2</v>
+        <v>3.73</v>
       </c>
       <c r="M26" t="n">
         <v>134.27</v>
       </c>
       <c r="N26" t="n">
-        <v>63.5</v>
+        <v>56.9</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1971,7 +1955,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2000,11 +1984,11 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sacred Ground</t>
+          <t>Rose Ghaiyyath (IRE)</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2014,16 +1998,16 @@
         <v>128</v>
       </c>
       <c r="K27" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L27" t="n">
-        <v>0.23</v>
+        <v>7.48</v>
       </c>
       <c r="M27" t="n">
         <v>134.27</v>
       </c>
       <c r="N27" t="n">
-        <v>62.9</v>
+        <v>49.4</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2031,7 +2015,7 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2060,11 +2044,11 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>Light Of Paris (GER)</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2074,16 +2058,16 @@
         <v>128</v>
       </c>
       <c r="K28" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.73</v>
+        <v>8.229999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>134.27</v>
       </c>
       <c r="N28" t="n">
-        <v>56.9</v>
+        <v>49.1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2120,11 +2104,11 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Rose Ghaiyyath (IRE)</t>
+          <t>Ourbren (IRE)</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2134,16 +2118,16 @@
         <v>128</v>
       </c>
       <c r="K29" t="n">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L29" t="n">
-        <v>7.48</v>
+        <v>8.979999999999999</v>
       </c>
       <c r="M29" t="n">
         <v>134.27</v>
       </c>
       <c r="N29" t="n">
-        <v>49.4</v>
+        <v>47</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2179,40 +2163,24 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" t="n">
-        <v>7</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Light Of Paris (GER)</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" t="n">
-        <v>128</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="M30" t="n">
-        <v>134.27</v>
-      </c>
-      <c r="N30" t="n">
-        <v>49.1</v>
-      </c>
+          <t>Capichera (IRE)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2239,40 +2207,24 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" t="n">
-        <v>8</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ourbren (IRE)</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>128</v>
-      </c>
-      <c r="K31" t="n">
-        <v>85</v>
-      </c>
-      <c r="L31" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="M31" t="n">
-        <v>134.27</v>
-      </c>
-      <c r="N31" t="n">
-        <v>47</v>
-      </c>
+          <t>Botagoz (IRE)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2300,34 +2252,36 @@
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Youthful King</t>
+          <t>In The Breeze (IRE)</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K32" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>216.42</v>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>82</v>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2356,34 +2310,38 @@
         <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Arc Zoosve</t>
+          <t>Maxident</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K33" t="n">
-        <v>79</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
       <c r="M33" t="n">
         <v>216.42</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>71.8</v>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2412,34 +2370,38 @@
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Alfred Boucher</t>
+          <t>Across Earth (IRE)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K34" t="n">
-        <v>88</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L34" t="n">
+        <v>13</v>
+      </c>
       <c r="M34" t="n">
         <v>216.42</v>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>55.6</v>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
@@ -2468,28 +2430,30 @@
         <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>In The Breeze (IRE)</t>
+          <t>Russian Rumour (IRE)</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="K35" t="n">
-        <v>87</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="L35" t="n">
+        <v>18.5</v>
+      </c>
       <c r="M35" t="n">
         <v>216.42</v>
       </c>
       <c r="N35" t="n">
-        <v>82</v>
+        <v>44.2</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2497,7 +2461,7 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="36">
@@ -2526,38 +2490,38 @@
         <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Maxident</t>
+          <t>Call My Bluff (IRE)</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J36" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K36" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>21.25</v>
       </c>
       <c r="M36" t="n">
         <v>216.42</v>
       </c>
       <c r="N36" t="n">
-        <v>71.8</v>
+        <v>62.4</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2586,38 +2550,38 @@
         <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Across Earth (IRE)</t>
+          <t>Hermetic</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K37" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>54.25</v>
       </c>
       <c r="M37" t="n">
         <v>216.42</v>
       </c>
       <c r="N37" t="n">
-        <v>55.6</v>
+        <v>47.7</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2645,40 +2609,24 @@
       <c r="F38" t="n">
         <v>3</v>
       </c>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Russian Rumour (IRE)</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>9</v>
-      </c>
-      <c r="J38" t="n">
-        <v>127</v>
-      </c>
-      <c r="K38" t="n">
-        <v>80</v>
-      </c>
-      <c r="L38" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>216.42</v>
-      </c>
-      <c r="N38" t="n">
-        <v>48.6</v>
-      </c>
+          <t>Youthful King</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P38" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2705,40 +2653,24 @@
       <c r="F39" t="n">
         <v>3</v>
       </c>
-      <c r="G39" t="n">
-        <v>5</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Call My Bluff (IRE)</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>9</v>
-      </c>
-      <c r="J39" t="n">
-        <v>131</v>
-      </c>
-      <c r="K39" t="n">
-        <v>84</v>
-      </c>
-      <c r="L39" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>216.42</v>
-      </c>
-      <c r="N39" t="n">
-        <v>62.4</v>
-      </c>
+          <t>Alfred Boucher</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2765,40 +2697,24 @@
       <c r="F40" t="n">
         <v>3</v>
       </c>
-      <c r="G40" t="n">
-        <v>6</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Hermetic</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J40" t="n">
-        <v>128</v>
-      </c>
-      <c r="K40" t="n">
-        <v>81</v>
-      </c>
-      <c r="L40" t="n">
-        <v>54.25</v>
-      </c>
-      <c r="M40" t="n">
-        <v>216.42</v>
-      </c>
-      <c r="N40" t="n">
-        <v>47.7</v>
-      </c>
+          <t>Arc Zoosve</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3184,34 +3100,36 @@
         <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Diamondonthehill</t>
+          <t>Rare Change (IRE)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K47" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>91.69</v>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>74.5</v>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
@@ -3240,28 +3158,30 @@
         <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Rare Change (IRE)</t>
+          <t>Dr Strangelove</t>
         </is>
       </c>
       <c r="I48" t="n">
         <v>4</v>
       </c>
       <c r="J48" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K48" t="n">
-        <v>82</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.03</v>
+      </c>
       <c r="M48" t="n">
         <v>91.69</v>
       </c>
       <c r="N48" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3269,7 +3189,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3298,30 +3218,30 @@
         <v>4</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Dr Strangelove</t>
+          <t>Blue Prince (IRE)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K49" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L49" t="n">
-        <v>0.03</v>
+        <v>1.28</v>
       </c>
       <c r="M49" t="n">
         <v>91.69</v>
       </c>
       <c r="N49" t="n">
-        <v>75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3329,7 +3249,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3358,30 +3278,30 @@
         <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Blue Prince (IRE)</t>
+          <t>Tronido</t>
         </is>
       </c>
       <c r="I50" t="n">
         <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K50" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L50" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="M50" t="n">
         <v>91.69</v>
       </c>
       <c r="N50" t="n">
-        <v>66.90000000000001</v>
+        <v>57.9</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3389,7 +3309,7 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
@@ -3418,30 +3338,30 @@
         <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tronido</t>
+          <t>Wobwobwob (IRE)</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J51" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K51" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="L51" t="n">
-        <v>1.78</v>
+        <v>2.53</v>
       </c>
       <c r="M51" t="n">
         <v>91.69</v>
       </c>
       <c r="N51" t="n">
-        <v>57.9</v>
+        <v>61.1</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3449,7 +3369,7 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3478,30 +3398,30 @@
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Wobwobwob (IRE)</t>
+          <t>Serenity Dream (IRE)</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="K52" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L52" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="M52" t="n">
         <v>91.69</v>
       </c>
       <c r="N52" t="n">
-        <v>61.1</v>
+        <v>51.5</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3509,7 +3429,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
@@ -3538,30 +3458,30 @@
         <v>4</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Serenity Dream (IRE)</t>
+          <t>Cherry Cobbler</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K53" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L53" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="M53" t="n">
         <v>91.69</v>
       </c>
       <c r="N53" t="n">
-        <v>51.5</v>
+        <v>57.4</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3569,7 +3489,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3598,30 +3518,30 @@
         <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Cherry Cobbler</t>
+          <t>Dannick</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K54" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L54" t="n">
-        <v>2.66</v>
+        <v>3.16</v>
       </c>
       <c r="M54" t="n">
         <v>91.69</v>
       </c>
       <c r="N54" t="n">
-        <v>57.4</v>
+        <v>50</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3629,7 +3549,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3657,40 +3577,24 @@
       <c r="F55" t="n">
         <v>4</v>
       </c>
-      <c r="G55" t="n">
-        <v>8</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Dannick</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" t="n">
-        <v>120</v>
-      </c>
-      <c r="K55" t="n">
-        <v>70</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="M55" t="n">
-        <v>91.69</v>
-      </c>
-      <c r="N55" t="n">
-        <v>50</v>
-      </c>
+          <t>Diamondonthehill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3716,18 +3620,18 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Rejoinder (IRE)</t>
+          <t>Cleodolinda (IRE)</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>2</v>
       </c>
       <c r="J56" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3736,14 +3640,16 @@
       <c r="M56" t="n">
         <v>61.17</v>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>72.3</v>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3770,11 +3676,11 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Cleodolinda (IRE)</t>
+          <t>Queenofthewild (IRE)</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3786,12 +3692,14 @@
       <c r="K57" t="n">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
       <c r="M57" t="n">
         <v>61.17</v>
       </c>
       <c r="N57" t="n">
-        <v>72.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3799,7 +3707,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
@@ -3826,30 +3734,30 @@
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Queenofthewild (IRE)</t>
+          <t>Hanney Boy (IRE)</t>
         </is>
       </c>
       <c r="I58" t="n">
         <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="M58" t="n">
         <v>61.17</v>
       </c>
       <c r="N58" t="n">
-        <v>67.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3857,7 +3765,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3884,30 +3792,30 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hanney Boy (IRE)</t>
+          <t>Away And Gone (IRE)</t>
         </is>
       </c>
       <c r="I59" t="n">
         <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="M59" t="n">
         <v>61.17</v>
       </c>
       <c r="N59" t="n">
-        <v>69.2</v>
+        <v>52.2</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3915,7 +3823,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3942,30 +3850,30 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Away And Gone (IRE)</t>
+          <t>Spirit Of Mann</t>
         </is>
       </c>
       <c r="I60" t="n">
         <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>5.1</v>
+        <v>7.35</v>
       </c>
       <c r="M60" t="n">
         <v>61.17</v>
       </c>
       <c r="N60" t="n">
-        <v>52.2</v>
+        <v>48.4</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4000,30 +3908,30 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Spirit Of Mann</t>
+          <t>Arrowstock (IRE)</t>
         </is>
       </c>
       <c r="I61" t="n">
         <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>7.35</v>
+        <v>7.5</v>
       </c>
       <c r="M61" t="n">
         <v>61.17</v>
       </c>
       <c r="N61" t="n">
-        <v>48.4</v>
+        <v>42.4</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4031,7 +3939,7 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
@@ -4058,30 +3966,30 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Arrowstock (IRE)</t>
+          <t>Howlin Wolf (IRE)</t>
         </is>
       </c>
       <c r="I62" t="n">
         <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>7.5</v>
+        <v>7.65</v>
       </c>
       <c r="M62" t="n">
         <v>61.17</v>
       </c>
       <c r="N62" t="n">
-        <v>42.4</v>
+        <v>44.4</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4089,7 +3997,7 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4116,11 +4024,11 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Howlin Wolf (IRE)</t>
+          <t>Desert Alchemist (IRE)</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4133,13 +4041,13 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>7.65</v>
+        <v>12.4</v>
       </c>
       <c r="M63" t="n">
         <v>61.17</v>
       </c>
       <c r="N63" t="n">
-        <v>44.4</v>
+        <v>25.1</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4147,7 +4055,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4174,34 +4082,34 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Desert Alchemist (IRE)</t>
+          <t>Come On Noddy (IRE)</t>
         </is>
       </c>
       <c r="I64" t="n">
         <v>2</v>
       </c>
       <c r="J64" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>12.4</v>
+        <v>45.4</v>
       </c>
       <c r="M64" t="n">
         <v>61.17</v>
       </c>
       <c r="N64" t="n">
-        <v>25.1</v>
+        <v>-27.9</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -4231,40 +4139,24 @@
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>9</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Come On Noddy (IRE)</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>2</v>
-      </c>
-      <c r="J65" t="n">
-        <v>133</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="M65" t="n">
-        <v>61.17</v>
-      </c>
-      <c r="N65" t="n">
-        <v>-28.8</v>
-      </c>
+          <t>Rejoinder (IRE)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4357,7 +4249,7 @@
         <v>8</v>
       </c>
       <c r="J67" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K67" t="n">
         <v>98</v>
@@ -4369,7 +4261,7 @@
         <v>59.92</v>
       </c>
       <c r="N67" t="n">
-        <v>87.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4377,7 +4269,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="68">
@@ -4435,7 +4327,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
@@ -4473,7 +4365,7 @@
         <v>3</v>
       </c>
       <c r="J69" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K69" t="n">
         <v>85</v>
@@ -4485,7 +4377,7 @@
         <v>59.92</v>
       </c>
       <c r="N69" t="n">
-        <v>66.7</v>
+        <v>62.3</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4694,34 +4586,36 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Alnofoor</t>
+          <t>Happy Henry (IRE)</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="K73" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>60.68</v>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>60.9</v>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-22.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="74">
@@ -4748,34 +4642,38 @@
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Polar Bear (IRE)</t>
+          <t>Hugos Girl (IRE)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>127</v>
       </c>
       <c r="K74" t="n">
-        <v>57</v>
-      </c>
-      <c r="L74" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M74" t="n">
         <v>60.68</v>
       </c>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="n">
+        <v>63.8</v>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>-22.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
@@ -4802,11 +4700,11 @@
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Happy Henry (IRE)</t>
+          <t>An Laochmor (IRE)</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4816,14 +4714,16 @@
         <v>120</v>
       </c>
       <c r="K75" t="n">
-        <v>50</v>
-      </c>
-      <c r="L75" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9</v>
+      </c>
       <c r="M75" t="n">
         <v>60.68</v>
       </c>
       <c r="N75" t="n">
-        <v>60.9</v>
+        <v>57.4</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4831,7 +4731,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="76">
@@ -4858,30 +4758,30 @@
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Hugos Girl (IRE)</t>
+          <t>Thurso</t>
         </is>
       </c>
       <c r="I76" t="n">
         <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K76" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="L76" t="n">
-        <v>0.75</v>
+        <v>2.4</v>
       </c>
       <c r="M76" t="n">
         <v>60.68</v>
       </c>
       <c r="N76" t="n">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -4889,7 +4789,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4916,30 +4816,30 @@
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>An Laochmor (IRE)</t>
+          <t>Sommelier</t>
         </is>
       </c>
       <c r="I77" t="n">
         <v>5</v>
       </c>
       <c r="J77" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="K77" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="L77" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="M77" t="n">
         <v>60.68</v>
       </c>
       <c r="N77" t="n">
-        <v>62.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -4947,7 +4847,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4974,30 +4874,30 @@
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Thurso</t>
+          <t>Ballysax Lil Mick (IRE)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J78" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="K78" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="L78" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M78" t="n">
         <v>60.68</v>
       </c>
       <c r="N78" t="n">
-        <v>69.2</v>
+        <v>51.1</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5005,7 +4905,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="79">
@@ -5032,30 +4932,30 @@
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sommelier</t>
+          <t>Mickey The Steel</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J79" t="n">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="K79" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="L79" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="M79" t="n">
         <v>60.68</v>
       </c>
       <c r="N79" t="n">
-        <v>70.8</v>
+        <v>57.1</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -5063,7 +4963,7 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -5090,30 +4990,30 @@
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Ballysax Lil Mick (IRE)</t>
+          <t>Jazzit</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J80" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K80" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="M80" t="n">
         <v>60.68</v>
       </c>
       <c r="N80" t="n">
-        <v>51.1</v>
+        <v>47.3</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5148,30 +5048,30 @@
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Mickey The Steel</t>
+          <t>Asdana (IRE)</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K81" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="L81" t="n">
-        <v>3.6</v>
+        <v>4.699999999999999</v>
       </c>
       <c r="M81" t="n">
         <v>60.68</v>
       </c>
       <c r="N81" t="n">
-        <v>58.4</v>
+        <v>56.7</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5179,7 +5079,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5206,30 +5106,30 @@
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Jazzit</t>
+          <t>Mint Man</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="K82" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L82" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="M82" t="n">
         <v>60.68</v>
       </c>
       <c r="N82" t="n">
-        <v>47.3</v>
+        <v>54.4</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5237,7 +5137,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5264,30 +5164,30 @@
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Asdana (IRE)</t>
+          <t>Jordan Breeze (IRE)</t>
         </is>
       </c>
       <c r="I83" t="n">
         <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="K83" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L83" t="n">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="M83" t="n">
         <v>60.68</v>
       </c>
       <c r="N83" t="n">
-        <v>56.7</v>
+        <v>42.1</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -5295,7 +5195,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="84">
@@ -5322,30 +5222,30 @@
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mint Man</t>
+          <t>Harrys Hill</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J84" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K84" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L84" t="n">
-        <v>5.7</v>
+        <v>6.749999999999999</v>
       </c>
       <c r="M84" t="n">
         <v>60.68</v>
       </c>
       <c r="N84" t="n">
-        <v>54.4</v>
+        <v>47.7</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5380,30 +5280,30 @@
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Jordan Breeze (IRE)</t>
+          <t>Jackie Jump Up</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K85" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="L85" t="n">
-        <v>5.75</v>
+        <v>7.499999999999999</v>
       </c>
       <c r="M85" t="n">
         <v>60.68</v>
       </c>
       <c r="N85" t="n">
-        <v>49</v>
+        <v>42.3</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -5411,7 +5311,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86">
@@ -5438,30 +5338,30 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Harrys Hill</t>
+          <t>Step Back In Time (IRE)</t>
         </is>
       </c>
       <c r="I86" t="n">
         <v>8</v>
       </c>
       <c r="J86" t="n">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="K86" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="L86" t="n">
-        <v>6.75</v>
+        <v>7.599999999999999</v>
       </c>
       <c r="M86" t="n">
         <v>60.68</v>
       </c>
       <c r="N86" t="n">
-        <v>50.7</v>
+        <v>35.8</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -5469,7 +5369,7 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="87">
@@ -5496,30 +5396,30 @@
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Jackie Jump Up</t>
+          <t>Astute Power (IRE)</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K87" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L87" t="n">
-        <v>7.5</v>
+        <v>7.699999999999999</v>
       </c>
       <c r="M87" t="n">
         <v>60.68</v>
       </c>
       <c r="N87" t="n">
-        <v>45.2</v>
+        <v>46.3</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -5527,7 +5427,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -5554,30 +5454,30 @@
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Step Back In Time (IRE)</t>
+          <t>Lethimfly (IRE)</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K88" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="L88" t="n">
-        <v>7.6</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M88" t="n">
         <v>60.68</v>
       </c>
       <c r="N88" t="n">
-        <v>35.8</v>
+        <v>45</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -5585,7 +5485,7 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
@@ -5612,30 +5512,30 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Astute Power (IRE)</t>
+          <t>Verified (IRE)</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K89" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="L89" t="n">
-        <v>7.7</v>
+        <v>8.999999999999998</v>
       </c>
       <c r="M89" t="n">
         <v>60.68</v>
       </c>
       <c r="N89" t="n">
-        <v>46.3</v>
+        <v>37</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -5643,7 +5543,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5670,30 +5570,30 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lethimfly (IRE)</t>
+          <t>Caffu Zafeen (IRE)</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K90" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L90" t="n">
-        <v>8.949999999999999</v>
+        <v>12.25</v>
       </c>
       <c r="M90" t="n">
         <v>60.68</v>
       </c>
       <c r="N90" t="n">
-        <v>45</v>
+        <v>26.9</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -5701,7 +5601,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5728,30 +5628,30 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Verified (IRE)</t>
+          <t>Plushy (IRE)</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="K91" t="n">
         <v>60</v>
       </c>
       <c r="L91" t="n">
-        <v>9</v>
+        <v>13.25</v>
       </c>
       <c r="M91" t="n">
         <v>60.68</v>
       </c>
       <c r="N91" t="n">
-        <v>37</v>
+        <v>8.9</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -5759,7 +5659,7 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5786,30 +5686,30 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Caffu Zafeen (IRE)</t>
+          <t>Viamonte (IRE)</t>
         </is>
       </c>
       <c r="I92" t="n">
         <v>5</v>
       </c>
       <c r="J92" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="K92" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L92" t="n">
-        <v>12.25</v>
+        <v>15</v>
       </c>
       <c r="M92" t="n">
         <v>60.68</v>
       </c>
       <c r="N92" t="n">
-        <v>26.9</v>
+        <v>7.2</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -5844,30 +5744,30 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Plushy (IRE)</t>
+          <t>Three Sixteen (IRE)</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="K93" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L93" t="n">
-        <v>13.25</v>
+        <v>18.75</v>
       </c>
       <c r="M93" t="n">
         <v>60.68</v>
       </c>
       <c r="N93" t="n">
-        <v>15.1</v>
+        <v>-3.7</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -5875,7 +5775,7 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5901,40 +5801,24 @@
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="n">
-        <v>20</v>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Viamonte (IRE)</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>5</v>
-      </c>
-      <c r="J94" t="n">
-        <v>131</v>
-      </c>
-      <c r="K94" t="n">
-        <v>61</v>
-      </c>
-      <c r="L94" t="n">
-        <v>15</v>
-      </c>
-      <c r="M94" t="n">
-        <v>60.68</v>
-      </c>
-      <c r="N94" t="n">
-        <v>15.3</v>
-      </c>
+          <t>Polar Bear (IRE)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P94" t="n">
-        <v>1</v>
-      </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5959,40 +5843,24 @@
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="n">
-        <v>21</v>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Three Sixteen (IRE)</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" t="n">
-        <v>134</v>
-      </c>
-      <c r="K95" t="n">
-        <v>64</v>
-      </c>
-      <c r="L95" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="M95" t="n">
-        <v>60.68</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-3.7</v>
-      </c>
+          <t>Alnofoor</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6018,34 +5886,36 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Oceans Breath (IRE)</t>
+          <t>Jon Riggens (IRE)</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J96" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="K96" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
         <v>71</v>
       </c>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>72.3</v>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="97">
@@ -6072,28 +5942,30 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Jon Riggens (IRE)</t>
+          <t>Alfred Tennyson (IRE)</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K97" t="n">
-        <v>71</v>
-      </c>
-      <c r="L97" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.05</v>
+      </c>
       <c r="M97" t="n">
         <v>71</v>
       </c>
       <c r="N97" t="n">
-        <v>72.3</v>
+        <v>74.7</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6101,7 +5973,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6128,30 +6000,30 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Alfred Tennyson (IRE)</t>
+          <t>Clonmacash</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J98" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K98" t="n">
         <v>75</v>
       </c>
       <c r="L98" t="n">
-        <v>0.05</v>
+        <v>1.3</v>
       </c>
       <c r="M98" t="n">
         <v>71</v>
       </c>
       <c r="N98" t="n">
-        <v>74.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6159,7 +6031,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6186,30 +6058,30 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Clonmacash</t>
+          <t>I Bid You Ajou (FR)</t>
         </is>
       </c>
       <c r="I99" t="n">
         <v>5</v>
       </c>
       <c r="J99" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K99" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L99" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="M99" t="n">
         <v>71</v>
       </c>
       <c r="N99" t="n">
-        <v>71.5</v>
+        <v>61.1</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6244,30 +6116,30 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>I Bid You Ajou (FR)</t>
+          <t>Collective Power (IRE)</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J100" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K100" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L100" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="M100" t="n">
         <v>71</v>
       </c>
       <c r="N100" t="n">
-        <v>66.5</v>
+        <v>55.4</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6302,30 +6174,30 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Collective Power (IRE)</t>
+          <t>Nouvel Espoir (IRE)</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J101" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K101" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L101" t="n">
-        <v>3.33</v>
+        <v>7.08</v>
       </c>
       <c r="M101" t="n">
         <v>71</v>
       </c>
       <c r="N101" t="n">
-        <v>63.9</v>
+        <v>43.1</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -6333,7 +6205,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="102">
@@ -6360,30 +6232,30 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Nouvel Espoir (IRE)</t>
+          <t>Gerrits Gem (IRE)</t>
         </is>
       </c>
       <c r="I102" t="n">
         <v>6</v>
       </c>
       <c r="J102" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K102" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="L102" t="n">
-        <v>7.08</v>
+        <v>7.58</v>
       </c>
       <c r="M102" t="n">
         <v>71</v>
       </c>
       <c r="N102" t="n">
-        <v>43.1</v>
+        <v>48.7</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -6391,7 +6263,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6418,30 +6290,30 @@
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
+        <v>8</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Greek Flower (IRE)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
         <v>7</v>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Gerrits Gem (IRE)</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>6</v>
-      </c>
       <c r="J103" t="n">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K103" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="L103" t="n">
-        <v>7.58</v>
+        <v>10.58</v>
       </c>
       <c r="M103" t="n">
         <v>71</v>
       </c>
       <c r="N103" t="n">
-        <v>55.6</v>
+        <v>36</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6449,7 +6321,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6476,30 +6348,30 @@
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Greek Flower (IRE)</t>
+          <t>Aurora Nova (IRE)</t>
         </is>
       </c>
       <c r="I104" t="n">
         <v>7</v>
       </c>
       <c r="J104" t="n">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="K104" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L104" t="n">
-        <v>10.58</v>
+        <v>16.08</v>
       </c>
       <c r="M104" t="n">
         <v>71</v>
       </c>
       <c r="N104" t="n">
-        <v>36</v>
+        <v>2.3</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6533,40 +6405,24 @@
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="n">
-        <v>9</v>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Aurora Nova (IRE)</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>7</v>
-      </c>
-      <c r="J105" t="n">
-        <v>127</v>
-      </c>
-      <c r="K105" t="n">
-        <v>66</v>
-      </c>
-      <c r="L105" t="n">
-        <v>16.08</v>
-      </c>
-      <c r="M105" t="n">
-        <v>71</v>
-      </c>
-      <c r="N105" t="n">
-        <v>9.300000000000001</v>
-      </c>
+          <t>Oceans Breath (IRE)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6592,34 +6448,36 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lady Lilac (IRE)</t>
+          <t>Isaac Newton (IRE)</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K106" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
         <v>113.81</v>
       </c>
-      <c r="N106" t="inlineStr"/>
+      <c r="N106" t="n">
+        <v>77.90000000000001</v>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>-11.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="107">
@@ -6646,34 +6504,38 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Lemsairbat (FR)</t>
+          <t>Geryon (IRE)</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K107" t="n">
-        <v>98</v>
-      </c>
-      <c r="L107" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M107" t="n">
         <v>113.81</v>
       </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="n">
+        <v>76.8</v>
+      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>-11.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="108">
@@ -6700,28 +6562,30 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Isaac Newton (IRE)</t>
+          <t>Hotazhell</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K108" t="n">
-        <v>103</v>
-      </c>
-      <c r="L108" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.18</v>
+      </c>
       <c r="M108" t="n">
         <v>113.81</v>
       </c>
       <c r="N108" t="n">
-        <v>77.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -6729,7 +6593,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -6756,30 +6620,30 @@
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Geryon (IRE)</t>
+          <t>Wemightakedlongway (IRE)</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K109" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="L109" t="n">
-        <v>0.15</v>
+        <v>2.18</v>
       </c>
       <c r="M109" t="n">
         <v>113.81</v>
       </c>
       <c r="N109" t="n">
-        <v>76.8</v>
+        <v>73.8</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6814,30 +6678,30 @@
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Hotazhell</t>
+          <t>Flushing Meadows (USA)</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K110" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="L110" t="n">
-        <v>0.18</v>
+        <v>2.93</v>
       </c>
       <c r="M110" t="n">
         <v>113.81</v>
       </c>
       <c r="N110" t="n">
-        <v>82.8</v>
+        <v>71.8</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -6845,7 +6709,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="111">
@@ -6872,30 +6736,30 @@
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Wemightakedlongway (IRE)</t>
+          <t>Bubble Gum (FR)</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J111" t="n">
         <v>130</v>
       </c>
       <c r="K111" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="L111" t="n">
-        <v>2.18</v>
+        <v>3.08</v>
       </c>
       <c r="M111" t="n">
         <v>113.81</v>
       </c>
       <c r="N111" t="n">
-        <v>73.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -6903,7 +6767,7 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="112">
@@ -6930,30 +6794,30 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Flushing Meadows (USA)</t>
+          <t>Hazdann (IRE)</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K112" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L112" t="n">
-        <v>2.93</v>
+        <v>3.23</v>
       </c>
       <c r="M112" t="n">
         <v>113.81</v>
       </c>
       <c r="N112" t="n">
-        <v>71.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -6961,7 +6825,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -6988,30 +6852,30 @@
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bubble Gum (FR)</t>
+          <t>Subsonic (IRE)</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
         <v>130</v>
       </c>
       <c r="K113" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L113" t="n">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="M113" t="n">
         <v>113.81</v>
       </c>
       <c r="N113" t="n">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -7019,7 +6883,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="114">
@@ -7046,30 +6910,30 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Hazdann (IRE)</t>
+          <t>Summer Is Tomorrow (IRE)</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K114" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="L114" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="M114" t="n">
         <v>113.81</v>
       </c>
       <c r="N114" t="n">
-        <v>74.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -7077,7 +6941,7 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="115">
@@ -7104,30 +6968,30 @@
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Subsonic (IRE)</t>
+          <t>Norwalk Havoc</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K115" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L115" t="n">
-        <v>3.26</v>
+        <v>4.91</v>
       </c>
       <c r="M115" t="n">
         <v>113.81</v>
       </c>
       <c r="N115" t="n">
-        <v>70.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -7135,7 +6999,7 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -7161,40 +7025,24 @@
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="n">
-        <v>9</v>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Summer Is Tomorrow (IRE)</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>3</v>
-      </c>
-      <c r="J116" t="n">
-        <v>124</v>
-      </c>
-      <c r="K116" t="n">
-        <v>92</v>
-      </c>
-      <c r="L116" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="M116" t="n">
-        <v>113.81</v>
-      </c>
-      <c r="N116" t="n">
-        <v>68.8</v>
-      </c>
+          <t>Lady Lilac (IRE)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P116" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7219,40 +7067,24 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="n">
-        <v>10</v>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Norwalk Havoc</t>
-        </is>
-      </c>
-      <c r="I117" t="n">
-        <v>5</v>
-      </c>
-      <c r="J117" t="n">
-        <v>138</v>
-      </c>
-      <c r="K117" t="n">
-        <v>103</v>
-      </c>
-      <c r="L117" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="M117" t="n">
-        <v>113.81</v>
-      </c>
-      <c r="N117" t="n">
-        <v>72.40000000000001</v>
-      </c>
+          <t>Lemsairbat (FR)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P117" t="n">
-        <v>4</v>
-      </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7278,34 +7110,36 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sanctijude (IRE)</t>
+          <t>Duckadilly (IRE)</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K118" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
         <v>102.8</v>
       </c>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="n">
+        <v>82</v>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>-10.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="119">
@@ -7332,11 +7166,11 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Quebec (GER)</t>
+          <t>Syzygy</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -7346,20 +7180,24 @@
         <v>135</v>
       </c>
       <c r="K119" t="n">
-        <v>97</v>
-      </c>
-      <c r="L119" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M119" t="n">
         <v>102.8</v>
       </c>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="n">
+        <v>80.5</v>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>-10.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="120">
@@ -7386,28 +7224,30 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sindria (IRE)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>4</v>
+      </c>
+      <c r="J120" t="n">
+        <v>138</v>
+      </c>
+      <c r="K120" t="n">
+        <v>100</v>
+      </c>
+      <c r="L120" t="n">
         <v>1</v>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Duckadilly (IRE)</t>
-        </is>
-      </c>
-      <c r="I120" t="n">
-        <v>5</v>
-      </c>
-      <c r="J120" t="n">
-        <v>135</v>
-      </c>
-      <c r="K120" t="n">
-        <v>98</v>
-      </c>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
         <v>102.8</v>
       </c>
       <c r="N120" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -7415,7 +7255,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -7442,30 +7282,30 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Syzygy</t>
+          <t>La Fogata (IRE)</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K121" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="L121" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="M121" t="n">
         <v>102.8</v>
       </c>
       <c r="N121" t="n">
-        <v>80.5</v>
+        <v>71.3</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -7473,7 +7313,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7500,30 +7340,30 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sindria (IRE)</t>
+          <t>Drop Dead Gorgeous (IRE)</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="K122" t="n">
         <v>100</v>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>4.75</v>
       </c>
       <c r="M122" t="n">
         <v>102.8</v>
       </c>
       <c r="N122" t="n">
-        <v>82.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -7531,7 +7371,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7558,30 +7398,30 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>La Fogata (IRE)</t>
+          <t>Yellowstone Lake (FR)</t>
         </is>
       </c>
       <c r="I123" t="n">
         <v>3</v>
       </c>
       <c r="J123" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K123" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="L123" t="n">
-        <v>1.75</v>
+        <v>6.5</v>
       </c>
       <c r="M123" t="n">
         <v>102.8</v>
       </c>
       <c r="N123" t="n">
-        <v>71.3</v>
+        <v>60</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -7589,7 +7429,7 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="124">
@@ -7616,30 +7456,30 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Drop Dead Gorgeous (IRE)</t>
+          <t>Fingerpaint</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K124" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L124" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="M124" t="n">
         <v>102.8</v>
       </c>
       <c r="N124" t="n">
-        <v>63.4</v>
+        <v>60</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -7647,7 +7487,7 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="125">
@@ -7674,30 +7514,30 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Yellowstone Lake (FR)</t>
+          <t>White Sand Beach (USA)</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>3</v>
       </c>
       <c r="J125" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K125" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L125" t="n">
-        <v>6.5</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M125" t="n">
         <v>102.8</v>
       </c>
       <c r="N125" t="n">
-        <v>60</v>
+        <v>53.8</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -7705,7 +7545,7 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7732,38 +7572,38 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Fingerpaint</t>
+          <t>Fast Tara (IRE)</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J126" t="n">
         <v>135</v>
       </c>
       <c r="K126" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="L126" t="n">
-        <v>9</v>
+        <v>20.05</v>
       </c>
       <c r="M126" t="n">
         <v>102.8</v>
       </c>
       <c r="N126" t="n">
-        <v>60</v>
+        <v>44.1</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7789,40 +7629,24 @@
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="n">
-        <v>8</v>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>White Sand Beach (USA)</t>
-        </is>
-      </c>
-      <c r="I127" t="n">
-        <v>3</v>
-      </c>
-      <c r="J127" t="n">
-        <v>124</v>
-      </c>
-      <c r="K127" t="n">
-        <v>82</v>
-      </c>
-      <c r="L127" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="M127" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="N127" t="n">
-        <v>53.8</v>
-      </c>
+          <t>Quebec (GER)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7847,40 +7671,24 @@
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="n">
-        <v>9</v>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Fast Tara (IRE)</t>
-        </is>
-      </c>
-      <c r="I128" t="n">
-        <v>6</v>
-      </c>
-      <c r="J128" t="n">
-        <v>135</v>
-      </c>
-      <c r="K128" t="n">
-        <v>78</v>
-      </c>
-      <c r="L128" t="n">
-        <v>20.05</v>
-      </c>
-      <c r="M128" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="N128" t="n">
-        <v>44.1</v>
-      </c>
+          <t>Sanctijude (IRE)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7917,7 +7725,7 @@
         <v>7</v>
       </c>
       <c r="J129" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K129" t="n">
         <v>41</v>
@@ -7927,7 +7735,7 @@
         <v>173.08</v>
       </c>
       <c r="N129" t="n">
-        <v>39</v>
+        <v>34.5</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -7935,7 +7743,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>-6.5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="130">
@@ -8147,7 +7955,7 @@
         <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K133" t="n">
         <v>50</v>
@@ -8159,7 +7967,7 @@
         <v>173.08</v>
       </c>
       <c r="N133" t="n">
-        <v>48.6</v>
+        <v>41.8</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -8167,7 +7975,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="134">
@@ -8205,7 +8013,7 @@
         <v>6</v>
       </c>
       <c r="J134" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K134" t="n">
         <v>31</v>
@@ -8217,7 +8025,7 @@
         <v>173.08</v>
       </c>
       <c r="N134" t="n">
-        <v>37.2</v>
+        <v>33.6</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -8327,7 +8135,7 @@
         <v>58</v>
       </c>
       <c r="L136" t="n">
-        <v>6.78</v>
+        <v>6.779999999999999</v>
       </c>
       <c r="M136" t="n">
         <v>173.08</v>
@@ -8341,7 +8149,7 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -8399,7 +8207,7 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
@@ -8457,7 +8265,7 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -8832,34 +8640,36 @@
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Appian Way (FR)</t>
+          <t>Jurality</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J145" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K145" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
         <v>171.73</v>
       </c>
-      <c r="N145" t="inlineStr"/>
+      <c r="N145" t="n">
+        <v>57</v>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>-15</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="146">
@@ -8886,28 +8696,30 @@
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Jurality</t>
+          <t>Synchronize (IRE)</t>
         </is>
       </c>
       <c r="I146" t="n">
         <v>5</v>
       </c>
       <c r="J146" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="K146" t="n">
-        <v>51</v>
-      </c>
-      <c r="L146" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="L146" t="n">
+        <v>2.25</v>
+      </c>
       <c r="M146" t="n">
         <v>171.73</v>
       </c>
       <c r="N146" t="n">
-        <v>57</v>
+        <v>38.3</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -8915,7 +8727,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="147">
@@ -8942,30 +8754,30 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Synchronize (IRE)</t>
+          <t>God Of Thunder (IRE)</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J147" t="n">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="K147" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L147" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M147" t="n">
         <v>171.73</v>
       </c>
       <c r="N147" t="n">
-        <v>44.6</v>
+        <v>58.1</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -8973,7 +8785,7 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -9000,30 +8812,30 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>God Of Thunder (IRE)</t>
+          <t>Felicity Smoak (IRE)</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="K148" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L148" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="M148" t="n">
         <v>171.73</v>
       </c>
       <c r="N148" t="n">
-        <v>58.1</v>
+        <v>52.9</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9031,7 +8843,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -9058,30 +8870,30 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Felicity Smoak (IRE)</t>
+          <t>Mystic Rose (IRE)</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>4</v>
       </c>
       <c r="J149" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K149" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L149" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="M149" t="n">
         <v>171.73</v>
       </c>
       <c r="N149" t="n">
-        <v>56.7</v>
+        <v>45.9</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -9089,7 +8901,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -9116,30 +8928,30 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Mystic Rose (IRE)</t>
+          <t>Mephisto (IRE)</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J150" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K150" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L150" t="n">
-        <v>5.15</v>
+        <v>7.4</v>
       </c>
       <c r="M150" t="n">
         <v>171.73</v>
       </c>
       <c r="N150" t="n">
-        <v>48</v>
+        <v>44.5</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -9174,30 +8986,30 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Mephisto (IRE)</t>
+          <t>Folly Beach</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J151" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K151" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L151" t="n">
-        <v>7.4</v>
+        <v>8.65</v>
       </c>
       <c r="M151" t="n">
         <v>171.73</v>
       </c>
       <c r="N151" t="n">
-        <v>44.5</v>
+        <v>46.3</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -9205,7 +9017,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -9232,30 +9044,30 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
+        <v>8</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Eastern Wind</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
         <v>7</v>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Folly Beach</t>
-        </is>
-      </c>
-      <c r="I152" t="n">
-        <v>8</v>
-      </c>
       <c r="J152" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="K152" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L152" t="n">
-        <v>8.65</v>
+        <v>9.9</v>
       </c>
       <c r="M152" t="n">
         <v>171.73</v>
       </c>
       <c r="N152" t="n">
-        <v>48.9</v>
+        <v>40.8</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -9263,7 +9075,7 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -9290,30 +9102,30 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Eastern Wind</t>
+          <t>Just Another Eagle (IRE)</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J153" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="K153" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="L153" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="M153" t="n">
         <v>171.73</v>
       </c>
       <c r="N153" t="n">
-        <v>45.8</v>
+        <v>31.1</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -9321,7 +9133,7 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154">
@@ -9348,30 +9160,30 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
+        <v>10</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Talking Tough (IRE)</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
         <v>9</v>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Just Another Eagle (IRE)</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>6</v>
-      </c>
       <c r="J154" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="K154" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L154" t="n">
-        <v>10.9</v>
+        <v>15.15</v>
       </c>
       <c r="M154" t="n">
         <v>171.73</v>
       </c>
       <c r="N154" t="n">
-        <v>38.3</v>
+        <v>13.5</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -9379,7 +9191,7 @@
         </is>
       </c>
       <c r="P154" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="155">
@@ -9406,38 +9218,38 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Talking Tough (IRE)</t>
+          <t>Nita (GER)</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J155" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="K155" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L155" t="n">
-        <v>15.15</v>
+        <v>22.15</v>
       </c>
       <c r="M155" t="n">
         <v>171.73</v>
       </c>
       <c r="N155" t="n">
-        <v>18.6</v>
+        <v>40.7</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
@@ -9464,30 +9276,30 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Nita (GER)</t>
+          <t>Creative Dancer (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J156" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="K156" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L156" t="n">
-        <v>22.15</v>
+        <v>26.15</v>
       </c>
       <c r="M156" t="n">
         <v>171.73</v>
       </c>
       <c r="N156" t="n">
-        <v>40.7</v>
+        <v>17.1</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9495,7 +9307,7 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
@@ -9522,30 +9334,30 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Creative Dancer (IRE)</t>
+          <t>Edge Of Darkness (IRE)</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J157" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K157" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L157" t="n">
-        <v>26.15</v>
+        <v>26.25</v>
       </c>
       <c r="M157" t="n">
         <v>171.73</v>
       </c>
       <c r="N157" t="n">
-        <v>17.1</v>
+        <v>28.2</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9553,7 +9365,7 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
@@ -9580,30 +9392,30 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Edge Of Darkness (IRE)</t>
+          <t>Cahir Bay (IRE)</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J158" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="K158" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="L158" t="n">
-        <v>26.25</v>
+        <v>49.25</v>
       </c>
       <c r="M158" t="n">
         <v>171.73</v>
       </c>
       <c r="N158" t="n">
-        <v>28.2</v>
+        <v>17.7</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -9637,40 +9449,24 @@
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="n">
-        <v>14</v>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Cahir Bay (IRE)</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>4</v>
-      </c>
-      <c r="J159" t="n">
-        <v>136</v>
-      </c>
-      <c r="K159" t="n">
-        <v>54</v>
-      </c>
-      <c r="L159" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="M159" t="n">
-        <v>171.73</v>
-      </c>
-      <c r="N159" t="n">
-        <v>17.7</v>
-      </c>
+          <t>Appian Way (FR)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P159" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
